--- a/survey_templates/035_outdoor_activity_safety_awareness_survey--survey_templates.xlsx
+++ b/survey_templates/035_outdoor_activity_safety_awareness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hiking</t>
+          <t>cycling</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hiking</t>
+          <t>Cycling</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cycling</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Swimming</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cycling</t>
+          <t>rock_climbing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cycling</t>
+          <t>Rock climbing</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>swimming</t>
+          <t>caving</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Swimming</t>
+          <t>Caving</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>swimming</t>
+          <t>rafting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Swimming</t>
+          <t>Rafting</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rock_climbing</t>
+          <t>horseback_riding</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rock climbing</t>
+          <t>Horseback Riding</t>
         </is>
       </c>
     </row>
@@ -905,63 +905,63 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>caving</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Caving</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>outdoor_habits_choices</t>
+          <t>safety_equipment_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rafting</t>
+          <t>helmet</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rafting</t>
+          <t>Helmet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>outdoor_habits_choices</t>
+          <t>safety_equipment_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>horseback_riding</t>
+          <t>first_aid_kit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Horseback Riding</t>
+          <t>First Aid Kit</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>outdoor_habits_choices</t>
+          <t>safety_equipment_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>emergency_whistle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Emergency Whistle</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>helmet</t>
+          <t>map_and_compass</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Helmet</t>
+          <t>Map and Compass</t>
         </is>
       </c>
     </row>
@@ -990,70 +990,70 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>first_aid_kit</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>First Aid Kit</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>safety_equipment_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>emergency_whistle</t>
+          <t>basic_wilderness_first_aid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Emergency Whistle</t>
+          <t>Basic Wilderness First Aid</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>safety_equipment_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>map_and_compass</t>
+          <t>wilderness_survival</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Map and Compass</t>
+          <t>Wilderness Survival</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>safety_equipment_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>first_aid_kit</t>
+          <t>map_and_compass_use</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>First Aid Kit</t>
+          <t>Map and Compass Use</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>safety_equipment_choices</t>
+          <t>training_needs_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1070,58 +1070,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>education_needs_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>basic_wilderness_first_aid</t>
+          <t>basic_outdoor_safety</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Basic Wilderness First Aid</t>
+          <t>Basic Outdoor Safety</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>education_needs_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wilderness_survival</t>
+          <t>safety_and_emergency_response</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wilderness Survival</t>
+          <t>Safety and Emergency Response</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>education_needs_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>map_and_compass_use</t>
+          <t>first_aid</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Map and Compass Use</t>
+          <t>First Aid</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>training_needs_choices</t>
+          <t>education_needs_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1130,74 +1130,6 @@
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>education_needs_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>basic_outdoor_safety</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Basic Outdoor Safety</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>education_needs_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>safety_and_emergency_response</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Safety and Emergency Response</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>education_needs_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>first_aid</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>First Aid</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>education_needs_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
